--- a/public/excel/test1.xlsx
+++ b/public/excel/test1.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\front\qqb-component\my-app\public\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F264613-D620-480A-B32D-1286EBB7F20E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22EF92DB-82A1-4E65-AECA-4BBCE639CCAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="海口市公安局" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,10 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="79">
-  <si>
-    <t>全局省外户籍流动人口采集情况统计表</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="73">
   <si>
     <t>序号</t>
   </si>
@@ -48,16 +45,7 @@
     <t>派出所</t>
   </si>
   <si>
-    <t>本周登记数</t>
-  </si>
-  <si>
-    <t>本周登记总数</t>
-  </si>
-  <si>
     <t>秀英分局</t>
-  </si>
-  <si>
-    <t>秀英所</t>
   </si>
   <si>
     <t>海秀所</t>
@@ -253,31 +241,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>周六（x.x）</t>
+    <t>x.x</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>周日（x.x）</t>
+    <t>秀英所</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>周一（x.x）</t>
+    <t>title</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>周二（x.x）</t>
+    <t>完成数</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>周三（x.x）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>周四（x.x）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>周五（x.x）</t>
+    <t>完成总数</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1355,7 +1335,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="27" t="s">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -1383,7 +1363,7 @@
     </row>
     <row r="3" spans="1:11" ht="26.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="33" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B3" s="34"/>
       <c r="C3" s="34"/>
@@ -1398,16 +1378,16 @@
     </row>
     <row r="4" spans="1:11" s="16" customFormat="1" ht="26.15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="36" t="s">
+      <c r="C4" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="36" t="s">
-        <v>3</v>
-      </c>
       <c r="D4" s="38" t="s">
-        <v>4</v>
+        <v>71</v>
       </c>
       <c r="E4" s="39"/>
       <c r="F4" s="39"/>
@@ -1422,28 +1402,28 @@
       <c r="B5" s="37"/>
       <c r="C5" s="37"/>
       <c r="D5" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="26.15" customHeight="1" x14ac:dyDescent="0.3">
@@ -1451,10 +1431,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -1471,7 +1451,7 @@
       </c>
       <c r="B7" s="25"/>
       <c r="C7" s="5" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -1488,7 +1468,7 @@
       </c>
       <c r="B8" s="25"/>
       <c r="C8" s="5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -1505,7 +1485,7 @@
       </c>
       <c r="B9" s="25"/>
       <c r="C9" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -1522,7 +1502,7 @@
       </c>
       <c r="B10" s="25"/>
       <c r="C10" s="8" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -1539,7 +1519,7 @@
       </c>
       <c r="B11" s="25"/>
       <c r="C11" s="5" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
@@ -1556,7 +1536,7 @@
       </c>
       <c r="B12" s="25"/>
       <c r="C12" s="8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -1573,7 +1553,7 @@
       </c>
       <c r="B13" s="25"/>
       <c r="C13" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -1590,7 +1570,7 @@
       </c>
       <c r="B14" s="25"/>
       <c r="C14" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -1607,7 +1587,7 @@
       </c>
       <c r="B15" s="25"/>
       <c r="C15" s="5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -1624,7 +1604,7 @@
       </c>
       <c r="B16" s="25"/>
       <c r="C16" s="5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
@@ -1641,7 +1621,7 @@
       </c>
       <c r="B17" s="25"/>
       <c r="C17" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -1658,7 +1638,7 @@
       </c>
       <c r="B18" s="26"/>
       <c r="C18" s="18" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D18" s="19"/>
       <c r="E18" s="19"/>
@@ -1674,10 +1654,10 @@
         <v>13</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
@@ -1694,7 +1674,7 @@
       </c>
       <c r="B20" s="25"/>
       <c r="C20" s="5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
@@ -1711,7 +1691,7 @@
       </c>
       <c r="B21" s="25"/>
       <c r="C21" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
@@ -1728,7 +1708,7 @@
       </c>
       <c r="B22" s="25"/>
       <c r="C22" s="5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
@@ -1745,7 +1725,7 @@
       </c>
       <c r="B23" s="25"/>
       <c r="C23" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
@@ -1762,7 +1742,7 @@
       </c>
       <c r="B24" s="25"/>
       <c r="C24" s="5" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
@@ -1779,7 +1759,7 @@
       </c>
       <c r="B25" s="25"/>
       <c r="C25" s="5" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
@@ -1796,7 +1776,7 @@
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
@@ -1813,7 +1793,7 @@
       </c>
       <c r="B27" s="25"/>
       <c r="C27" s="5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
@@ -1830,7 +1810,7 @@
       </c>
       <c r="B28" s="25"/>
       <c r="C28" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
@@ -1847,7 +1827,7 @@
       </c>
       <c r="B29" s="25"/>
       <c r="C29" s="5" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
@@ -1864,7 +1844,7 @@
       </c>
       <c r="B30" s="25"/>
       <c r="C30" s="5" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
@@ -1881,7 +1861,7 @@
       </c>
       <c r="B31" s="25"/>
       <c r="C31" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
@@ -1898,7 +1878,7 @@
       </c>
       <c r="B32" s="26"/>
       <c r="C32" s="21" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D32" s="22"/>
       <c r="E32" s="22"/>
@@ -1914,10 +1894,10 @@
         <v>26</v>
       </c>
       <c r="B33" s="24" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D33" s="10"/>
       <c r="E33" s="10"/>
@@ -1934,7 +1914,7 @@
       </c>
       <c r="B34" s="25"/>
       <c r="C34" s="9" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D34" s="10"/>
       <c r="E34" s="10"/>
@@ -1951,7 +1931,7 @@
       </c>
       <c r="B35" s="25"/>
       <c r="C35" s="9" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D35" s="10"/>
       <c r="E35" s="10"/>
@@ -1968,7 +1948,7 @@
       </c>
       <c r="B36" s="25"/>
       <c r="C36" s="9" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D36" s="10"/>
       <c r="E36" s="10"/>
@@ -1985,7 +1965,7 @@
       </c>
       <c r="B37" s="25"/>
       <c r="C37" s="9" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D37" s="10"/>
       <c r="E37" s="10"/>
@@ -2002,7 +1982,7 @@
       </c>
       <c r="B38" s="25"/>
       <c r="C38" s="9" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D38" s="10"/>
       <c r="E38" s="10"/>
@@ -2019,7 +1999,7 @@
       </c>
       <c r="B39" s="25"/>
       <c r="C39" s="9" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D39" s="10"/>
       <c r="E39" s="10"/>
@@ -2036,7 +2016,7 @@
       </c>
       <c r="B40" s="25"/>
       <c r="C40" s="9" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D40" s="10"/>
       <c r="E40" s="10"/>
@@ -2053,7 +2033,7 @@
       </c>
       <c r="B41" s="25"/>
       <c r="C41" s="9" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D41" s="10"/>
       <c r="E41" s="10"/>
@@ -2070,7 +2050,7 @@
       </c>
       <c r="B42" s="25"/>
       <c r="C42" s="9" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D42" s="10"/>
       <c r="E42" s="10"/>
@@ -2087,7 +2067,7 @@
       </c>
       <c r="B43" s="25"/>
       <c r="C43" s="9" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D43" s="10"/>
       <c r="E43" s="10"/>
@@ -2104,7 +2084,7 @@
       </c>
       <c r="B44" s="25"/>
       <c r="C44" s="9" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D44" s="10"/>
       <c r="E44" s="10"/>
@@ -2121,7 +2101,7 @@
       </c>
       <c r="B45" s="25"/>
       <c r="C45" s="9" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D45" s="12"/>
       <c r="E45" s="12"/>
@@ -2138,7 +2118,7 @@
       </c>
       <c r="B46" s="25"/>
       <c r="C46" s="9" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D46" s="12"/>
       <c r="E46" s="12"/>
@@ -2155,7 +2135,7 @@
       </c>
       <c r="B47" s="26"/>
       <c r="C47" s="21" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D47" s="23"/>
       <c r="E47" s="23"/>
@@ -2171,10 +2151,10 @@
         <v>40</v>
       </c>
       <c r="B48" s="24" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D48" s="10"/>
       <c r="E48" s="10"/>
@@ -2191,7 +2171,7 @@
       </c>
       <c r="B49" s="25"/>
       <c r="C49" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D49" s="10"/>
       <c r="E49" s="10"/>
@@ -2208,7 +2188,7 @@
       </c>
       <c r="B50" s="25"/>
       <c r="C50" s="5" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D50" s="10"/>
       <c r="E50" s="10"/>
@@ -2225,7 +2205,7 @@
       </c>
       <c r="B51" s="25"/>
       <c r="C51" s="5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="D51" s="10"/>
       <c r="E51" s="10"/>
@@ -2242,7 +2222,7 @@
       </c>
       <c r="B52" s="25"/>
       <c r="C52" s="5" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D52" s="10"/>
       <c r="E52" s="10"/>
@@ -2259,7 +2239,7 @@
       </c>
       <c r="B53" s="25"/>
       <c r="C53" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D53" s="10"/>
       <c r="E53" s="10"/>
@@ -2276,7 +2256,7 @@
       </c>
       <c r="B54" s="25"/>
       <c r="C54" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D54" s="10"/>
       <c r="E54" s="10"/>
@@ -2293,7 +2273,7 @@
       </c>
       <c r="B55" s="25"/>
       <c r="C55" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D55" s="10"/>
       <c r="E55" s="10"/>
@@ -2310,7 +2290,7 @@
       </c>
       <c r="B56" s="25"/>
       <c r="C56" s="5" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D56" s="10"/>
       <c r="E56" s="10"/>
@@ -2327,7 +2307,7 @@
       </c>
       <c r="B57" s="25"/>
       <c r="C57" s="5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D57" s="10"/>
       <c r="E57" s="10"/>
@@ -2344,7 +2324,7 @@
       </c>
       <c r="B58" s="25"/>
       <c r="C58" s="5" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D58" s="10"/>
       <c r="E58" s="10"/>
@@ -2361,7 +2341,7 @@
       </c>
       <c r="B59" s="25"/>
       <c r="C59" s="5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D59" s="10"/>
       <c r="E59" s="10"/>
@@ -2378,7 +2358,7 @@
       </c>
       <c r="B60" s="25"/>
       <c r="C60" s="5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D60" s="10"/>
       <c r="E60" s="10"/>
@@ -2395,7 +2375,7 @@
       </c>
       <c r="B61" s="25"/>
       <c r="C61" s="5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D61" s="10"/>
       <c r="E61" s="10"/>
@@ -2412,7 +2392,7 @@
       </c>
       <c r="B62" s="25"/>
       <c r="C62" s="5" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D62" s="10"/>
       <c r="E62" s="10"/>
@@ -2429,7 +2409,7 @@
       </c>
       <c r="B63" s="25"/>
       <c r="C63" s="5" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D63" s="10"/>
       <c r="E63" s="10"/>
@@ -2446,7 +2426,7 @@
       </c>
       <c r="B64" s="25"/>
       <c r="C64" s="5" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D64" s="10"/>
       <c r="E64" s="10"/>
@@ -2463,7 +2443,7 @@
       </c>
       <c r="B65" s="25"/>
       <c r="C65" s="5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D65" s="10"/>
       <c r="E65" s="10"/>
@@ -2480,7 +2460,7 @@
       </c>
       <c r="B66" s="25"/>
       <c r="C66" s="5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D66" s="10"/>
       <c r="E66" s="10"/>
@@ -2497,7 +2477,7 @@
       </c>
       <c r="B67" s="25"/>
       <c r="C67" s="5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D67" s="12"/>
       <c r="E67" s="12"/>
@@ -2514,7 +2494,7 @@
       </c>
       <c r="B68" s="25"/>
       <c r="C68" s="5" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D68" s="10"/>
       <c r="E68" s="10"/>
@@ -2531,7 +2511,7 @@
       </c>
       <c r="B69" s="26"/>
       <c r="C69" s="18" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D69" s="23"/>
       <c r="E69" s="23"/>
